--- a/database/event/3564/event_3564_evp_summary.xlsx
+++ b/database/event/3564/event_3564_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>7.2795</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3.7173</v>
       </c>
       <c r="D2" t="n">
         <v>2.5194</v>
@@ -545,7 +545,7 @@
         <v>6.9253</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.5364</v>
       </c>
       <c r="D3" t="n">
         <v>2.3763</v>
@@ -591,7 +591,7 @@
         <v>5.4782</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.7974</v>
       </c>
       <c r="D4" t="n">
         <v>1.7917</v>
@@ -637,7 +637,7 @@
         <v>5.3398</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.7268</v>
       </c>
       <c r="D5" t="n">
         <v>1.7358</v>
@@ -683,7 +683,7 @@
         <v>4.8614</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.4825</v>
       </c>
       <c r="D6" t="n">
         <v>1.5425</v>
@@ -729,7 +729,7 @@
         <v>4.2565</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.1736</v>
       </c>
       <c r="D7" t="n">
         <v>1.2982</v>
@@ -775,7 +775,7 @@
         <v>4.1475</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="D8" t="n">
         <v>1.2541</v>
@@ -821,7 +821,7 @@
         <v>3.9495</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.0168</v>
       </c>
       <c r="D9" t="n">
         <v>1.1741</v>
@@ -867,7 +867,7 @@
         <v>3.8354</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.9586</v>
       </c>
       <c r="D10" t="n">
         <v>1.1281</v>
@@ -913,7 +913,7 @@
         <v>3.8321</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.9569</v>
       </c>
       <c r="D11" t="n">
         <v>1.1267</v>
@@ -959,7 +959,7 @@
         <v>3.6989</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.8888</v>
       </c>
       <c r="D12" t="n">
         <v>1.0729</v>
@@ -1005,7 +1005,7 @@
         <v>3.5716</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.8238</v>
       </c>
       <c r="D13" t="n">
         <v>1.0215</v>
@@ -1051,7 +1051,7 @@
         <v>3.5245</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.7998</v>
       </c>
       <c r="D14" t="n">
         <v>1.0025</v>
@@ -1097,7 +1097,7 @@
         <v>3.1028</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.5844</v>
       </c>
       <c r="D15" t="n">
         <v>0.8321</v>
@@ -1143,7 +1143,7 @@
         <v>3.0471</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.556</v>
       </c>
       <c r="D16" t="n">
         <v>0.8096</v>
@@ -1189,7 +1189,7 @@
         <v>2.8115</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.4357</v>
       </c>
       <c r="D17" t="n">
         <v>0.7144</v>
@@ -1235,7 +1235,7 @@
         <v>2.6399</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.3481</v>
       </c>
       <c r="D18" t="n">
         <v>0.6451</v>
@@ -1281,7 +1281,7 @@
         <v>2.3912</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="D19" t="n">
         <v>0.5446</v>
@@ -1327,7 +1327,7 @@
         <v>2.0765</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.0604</v>
       </c>
       <c r="D20" t="n">
         <v>0.4175</v>
@@ -1373,7 +1373,7 @@
         <v>2.0617</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.0528</v>
       </c>
       <c r="D21" t="n">
         <v>0.4115</v>
@@ -1419,7 +1419,7 @@
         <v>1.8395</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.9393</v>
       </c>
       <c r="D22" t="n">
         <v>0.3218</v>
@@ -1465,7 +1465,7 @@
         <v>1.7086</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="D23" t="n">
         <v>0.2689</v>
@@ -1511,7 +1511,7 @@
         <v>1.6916</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.8638</v>
       </c>
       <c r="D24" t="n">
         <v>0.262</v>
@@ -1557,7 +1557,7 @@
         <v>1.6457</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.8404</v>
       </c>
       <c r="D25" t="n">
         <v>0.2435</v>
@@ -1603,7 +1603,7 @@
         <v>1.5134</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.7728</v>
       </c>
       <c r="D26" t="n">
         <v>0.19</v>
@@ -1649,7 +1649,7 @@
         <v>1.4115</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.7208</v>
       </c>
       <c r="D27" t="n">
         <v>0.1489</v>
@@ -1695,7 +1695,7 @@
         <v>1.4014</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.7156</v>
       </c>
       <c r="D28" t="n">
         <v>0.1448</v>
@@ -1741,7 +1741,7 @@
         <v>1.2464</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.6365</v>
       </c>
       <c r="D29" t="n">
         <v>0.0822</v>
@@ -1787,7 +1787,7 @@
         <v>1.2315</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="D30" t="n">
         <v>0.0761</v>
@@ -1833,7 +1833,7 @@
         <v>1.1667</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.5958</v>
       </c>
       <c r="D31" t="n">
         <v>0.05</v>
@@ -1879,7 +1879,7 @@
         <v>1.1044</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D32" t="n">
         <v>0.0248</v>
@@ -1925,7 +1925,7 @@
         <v>1.0015</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.5114</v>
       </c>
       <c r="D33" t="n">
         <v>-0.0168</v>
@@ -1971,7 +1971,7 @@
         <v>0.9986</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.5099</v>
       </c>
       <c r="D34" t="n">
         <v>-0.018</v>
@@ -2017,7 +2017,7 @@
         <v>0.9862</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.5036</v>
       </c>
       <c r="D35" t="n">
         <v>-0.023</v>
@@ -2063,7 +2063,7 @@
         <v>0.8891</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.454</v>
       </c>
       <c r="D36" t="n">
         <v>-0.0622</v>
@@ -2109,7 +2109,7 @@
         <v>0.7954</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.4062</v>
       </c>
       <c r="D37" t="n">
         <v>-0.1</v>
@@ -2155,7 +2155,7 @@
         <v>0.7435</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.3797</v>
       </c>
       <c r="D38" t="n">
         <v>-0.121</v>
@@ -2201,7 +2201,7 @@
         <v>0.4934</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.252</v>
       </c>
       <c r="D39" t="n">
         <v>-0.222</v>
@@ -2247,7 +2247,7 @@
         <v>0.4794</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.2448</v>
       </c>
       <c r="D40" t="n">
         <v>-0.2277</v>
@@ -2293,7 +2293,7 @@
         <v>0.3596</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.1836</v>
       </c>
       <c r="D41" t="n">
         <v>-0.2761</v>
@@ -2339,7 +2339,7 @@
         <v>0.2779</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.1419</v>
       </c>
       <c r="D42" t="n">
         <v>-0.3091</v>
@@ -2385,7 +2385,7 @@
         <v>0.2284</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.1166</v>
       </c>
       <c r="D43" t="n">
         <v>-0.3291</v>
@@ -2431,7 +2431,7 @@
         <v>0.1075</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.0549</v>
       </c>
       <c r="D44" t="n">
         <v>-0.3779</v>
@@ -2477,7 +2477,7 @@
         <v>0.08749999999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.0447</v>
       </c>
       <c r="D45" t="n">
         <v>-0.386</v>
@@ -2523,7 +2523,7 @@
         <v>-0.1095</v>
       </c>
       <c r="C46" t="n">
-        <v>-0</v>
+        <v>-0.0559</v>
       </c>
       <c r="D46" t="n">
         <v>-0.4656</v>
@@ -2569,7 +2569,7 @@
         <v>-0.121</v>
       </c>
       <c r="C47" t="n">
-        <v>-0</v>
+        <v>-0.0618</v>
       </c>
       <c r="D47" t="n">
         <v>-0.4702</v>
@@ -2615,7 +2615,7 @@
         <v>-0.1733</v>
       </c>
       <c r="C48" t="n">
-        <v>-0</v>
+        <v>-0.0885</v>
       </c>
       <c r="D48" t="n">
         <v>-0.4914</v>
@@ -2661,7 +2661,7 @@
         <v>-0.1787</v>
       </c>
       <c r="C49" t="n">
-        <v>-0</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4936</v>
@@ -2707,7 +2707,7 @@
         <v>-0.1996</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.1019</v>
       </c>
       <c r="D50" t="n">
         <v>-0.502</v>
@@ -2753,7 +2753,7 @@
         <v>-0.2224</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.1136</v>
       </c>
       <c r="D51" t="n">
         <v>-0.5112</v>
@@ -2799,7 +2799,7 @@
         <v>-0.2348</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.1199</v>
       </c>
       <c r="D52" t="n">
         <v>-0.5162</v>
@@ -2845,7 +2845,7 @@
         <v>-0.2456</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1254</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5206</v>
@@ -2891,7 +2891,7 @@
         <v>-0.2671</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1364</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5293</v>
@@ -2937,7 +2937,7 @@
         <v>-0.2909</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1485</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5389</v>
@@ -2983,7 +2983,7 @@
         <v>-0.3032</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1548</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5438</v>
@@ -3029,7 +3029,7 @@
         <v>-0.4117</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.2102</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5877</v>
@@ -3075,7 +3075,7 @@
         <v>-0.4863</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2483</v>
       </c>
       <c r="D58" t="n">
         <v>-0.6178</v>
@@ -3121,7 +3121,7 @@
         <v>-0.5785</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2954</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6551</v>
@@ -3167,7 +3167,7 @@
         <v>-0.6623</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.3382</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6889</v>
@@ -3213,7 +3213,7 @@
         <v>-0.6898</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.3522</v>
       </c>
       <c r="D61" t="n">
         <v>-0.7</v>
@@ -3259,7 +3259,7 @@
         <v>-0.746</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.3809</v>
       </c>
       <c r="D62" t="n">
         <v>-0.7227</v>
@@ -3305,7 +3305,7 @@
         <v>-0.8125</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.4149</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7496</v>
@@ -3351,7 +3351,7 @@
         <v>-0.8481</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.4331</v>
       </c>
       <c r="D64" t="n">
         <v>-0.764</v>
@@ -3397,7 +3397,7 @@
         <v>-0.9341</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.477</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7987</v>
@@ -3443,7 +3443,7 @@
         <v>-0.9751</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.4979</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8153</v>
@@ -3489,7 +3489,7 @@
         <v>-0.9878</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.5044</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8204</v>
@@ -3535,7 +3535,7 @@
         <v>-1.0454</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="D68" t="n">
         <v>-0.8437</v>
@@ -3581,7 +3581,7 @@
         <v>-1.3247</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.6765</v>
       </c>
       <c r="D69" t="n">
         <v>-0.9565</v>
@@ -3627,7 +3627,7 @@
         <v>-1.4213</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.7258</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9955000000000001</v>
@@ -3673,7 +3673,7 @@
         <v>-1.5431</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.788</v>
       </c>
       <c r="D71" t="n">
         <v>-1.0447</v>
@@ -3719,7 +3719,7 @@
         <v>-1.6451</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.8401</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0859</v>
@@ -3765,7 +3765,7 @@
         <v>-1.8068</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.9226</v>
       </c>
       <c r="D73" t="n">
         <v>-1.1513</v>
@@ -3811,7 +3811,7 @@
         <v>-1.834</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.9365</v>
       </c>
       <c r="D74" t="n">
         <v>-1.1623</v>
@@ -3857,7 +3857,7 @@
         <v>-2.1383</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.0919</v>
       </c>
       <c r="D75" t="n">
         <v>-1.2852</v>
@@ -3903,7 +3903,7 @@
         <v>-2.1531</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.0995</v>
       </c>
       <c r="D76" t="n">
         <v>-1.2912</v>
@@ -3949,7 +3949,7 @@
         <v>-2.2241</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.1357</v>
       </c>
       <c r="D77" t="n">
         <v>-1.3198</v>
@@ -3995,7 +3995,7 @@
         <v>-2.2915</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.1702</v>
       </c>
       <c r="D78" t="n">
         <v>-1.3471</v>
@@ -4041,7 +4041,7 @@
         <v>-2.36</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.2051</v>
       </c>
       <c r="D79" t="n">
         <v>-1.3747</v>
@@ -4087,7 +4087,7 @@
         <v>-2.3871</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.219</v>
       </c>
       <c r="D80" t="n">
         <v>-1.3857</v>
@@ -4133,7 +4133,7 @@
         <v>-2.5636</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-1.3091</v>
       </c>
       <c r="D81" t="n">
         <v>-1.457</v>

--- a/database/event/3564/event_3564_evp_summary.xlsx
+++ b/database/event/3564/event_3564_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.2795</v>
+        <v>8.478199999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7173</v>
+        <v>4.3294</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5194</v>
+        <v>2.9338</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2795</v>
+        <v>8.478199999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8433</v>
+        <v>4.042</v>
       </c>
       <c r="G2" t="n">
         <v>4.4362</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8433</v>
+        <v>4.042</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8433</v>
+        <v>4.042</v>
       </c>
       <c r="J2" t="n">
         <v>4.4362</v>
@@ -529,7 +529,7 @@
         <v>134</v>
       </c>
       <c r="M2" t="n">
-        <v>7.279500000000001</v>
+        <v>8.478200000000001</v>
       </c>
       <c r="N2" t="n">
         <v>239</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9253</v>
+        <v>7.9363</v>
       </c>
       <c r="C3" t="n">
-        <v>3.5364</v>
+        <v>4.0527</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3763</v>
+        <v>2.7179</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9253</v>
+        <v>7.9363</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9087</v>
+        <v>3.9197</v>
       </c>
       <c r="G3" t="n">
         <v>4.0166</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9087</v>
+        <v>3.9197</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9087</v>
+        <v>3.9197</v>
       </c>
       <c r="J3" t="n">
         <v>4.0166</v>
@@ -575,7 +575,7 @@
         <v>134</v>
       </c>
       <c r="M3" t="n">
-        <v>6.9253</v>
+        <v>7.936300000000001</v>
       </c>
       <c r="N3" t="n">
         <v>239</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4782</v>
+        <v>6.717</v>
       </c>
       <c r="C4" t="n">
-        <v>2.7974</v>
+        <v>3.43</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7917</v>
+        <v>2.2321</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4782</v>
+        <v>6.717</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6774</v>
+        <v>4.0742</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8008</v>
+        <v>2.6428</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6774</v>
+        <v>4.0853</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6774</v>
+        <v>4.0853</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8008</v>
+        <v>2.6428</v>
       </c>
       <c r="K4" t="n">
         <v>100</v>
@@ -621,7 +621,7 @@
         <v>152</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4782</v>
+        <v>6.7281</v>
       </c>
       <c r="N4" t="n">
         <v>252</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3398</v>
+        <v>6.4083</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7268</v>
+        <v>3.2724</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7358</v>
+        <v>2.1092</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3398</v>
+        <v>6.4083</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7597</v>
+        <v>2.8281</v>
       </c>
       <c r="G5" t="n">
         <v>3.5802</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7597</v>
+        <v>2.8281</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7597</v>
+        <v>2.8281</v>
       </c>
       <c r="J5" t="n">
         <v>3.5802</v>
@@ -667,7 +667,7 @@
         <v>152</v>
       </c>
       <c r="M5" t="n">
-        <v>5.3399</v>
+        <v>6.408300000000001</v>
       </c>
       <c r="N5" t="n">
         <v>252</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8614</v>
+        <v>6.2967</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4825</v>
+        <v>3.2154</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5425</v>
+        <v>2.0647</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8614</v>
+        <v>6.2967</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2186</v>
+        <v>2.4959</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6428</v>
+        <v>3.8008</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2186</v>
+        <v>2.4959</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2186</v>
+        <v>2.4959</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6428</v>
+        <v>3.8008</v>
       </c>
       <c r="K6" t="n">
         <v>100</v>
@@ -713,7 +713,7 @@
         <v>152</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8614</v>
+        <v>6.2967</v>
       </c>
       <c r="N6" t="n">
         <v>252</v>
@@ -722,81 +722,81 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2565</v>
+        <v>4.9291</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1736</v>
+        <v>2.517</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2982</v>
+        <v>1.5198</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2565</v>
+        <v>4.9291</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6269</v>
+        <v>2.9121</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6296</v>
+        <v>2.017</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6269</v>
+        <v>2.9121</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6269</v>
+        <v>2.9121</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6296</v>
+        <v>2.017</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L7" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2565</v>
+        <v>4.9291</v>
       </c>
       <c r="N7" t="n">
-        <v>252</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1475</v>
+        <v>4.8327</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1179</v>
+        <v>2.4678</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2541</v>
+        <v>1.4814</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1475</v>
+        <v>4.8327</v>
       </c>
       <c r="F8" t="n">
-        <v>2.177</v>
+        <v>3.654</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9705</v>
+        <v>1.1787</v>
       </c>
       <c r="H8" t="n">
-        <v>2.177</v>
+        <v>3.654</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1871</v>
+        <v>3.6848</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9705</v>
+        <v>1.1787</v>
       </c>
       <c r="K8" t="n">
         <v>174</v>
@@ -805,7 +805,7 @@
         <v>95</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1576</v>
+        <v>4.8635</v>
       </c>
       <c r="N8" t="n">
         <v>269</v>
@@ -814,277 +814,277 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9495</v>
+        <v>4.6953</v>
       </c>
       <c r="C9" t="n">
-        <v>2.0168</v>
+        <v>2.3977</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1741</v>
+        <v>1.4267</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9495</v>
+        <v>4.6953</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9325</v>
+        <v>3.1468</v>
       </c>
       <c r="G9" t="n">
-        <v>2.017</v>
+        <v>1.5485</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9325</v>
+        <v>3.1468</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9325</v>
+        <v>3.1468</v>
       </c>
       <c r="J9" t="n">
-        <v>2.017</v>
+        <v>1.5485</v>
       </c>
       <c r="K9" t="n">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="L9" t="n">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9495</v>
+        <v>4.6953</v>
       </c>
       <c r="N9" t="n">
-        <v>239</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.8354</v>
+        <v>4.5305</v>
       </c>
       <c r="C10" t="n">
-        <v>1.9586</v>
+        <v>2.3135</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1281</v>
+        <v>1.361</v>
       </c>
       <c r="E10" t="n">
-        <v>3.8354</v>
+        <v>4.5305</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2869</v>
+        <v>2.56</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5485</v>
+        <v>1.9705</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2869</v>
+        <v>2.56</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2869</v>
+        <v>2.5815</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5485</v>
+        <v>1.9705</v>
       </c>
       <c r="K10" t="n">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="L10" t="n">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8354</v>
+        <v>4.552</v>
       </c>
       <c r="N10" t="n">
-        <v>206</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8321</v>
+        <v>4.3281</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9569</v>
+        <v>2.2101</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1267</v>
+        <v>1.2804</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8321</v>
+        <v>4.3281</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1192</v>
+        <v>0.6985</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7129</v>
+        <v>3.6296</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1192</v>
+        <v>0.6985</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1192</v>
+        <v>0.6985</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7129</v>
+        <v>3.6296</v>
       </c>
       <c r="K11" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="M11" t="n">
-        <v>3.832100000000001</v>
+        <v>4.3281</v>
       </c>
       <c r="N11" t="n">
-        <v>206</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6989</v>
+        <v>4.3243</v>
       </c>
       <c r="C12" t="n">
-        <v>1.8888</v>
+        <v>2.2082</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0729</v>
+        <v>1.2789</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6989</v>
+        <v>4.3243</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4936</v>
+        <v>3.9011</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2053</v>
+        <v>0.4232</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4936</v>
+        <v>3.9011</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5052</v>
+        <v>3.9339</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2053</v>
+        <v>0.4232</v>
       </c>
       <c r="K12" t="n">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="L12" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7105</v>
+        <v>4.3571</v>
       </c>
       <c r="N12" t="n">
-        <v>283</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5716</v>
+        <v>4.2269</v>
       </c>
       <c r="C13" t="n">
-        <v>1.8238</v>
+        <v>2.1585</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0215</v>
+        <v>1.2401</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5716</v>
+        <v>4.2269</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3929</v>
+        <v>2.514</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1787</v>
+        <v>1.7129</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3929</v>
+        <v>2.514</v>
       </c>
       <c r="I13" t="n">
-        <v>2.404</v>
+        <v>2.514</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1787</v>
+        <v>1.7129</v>
       </c>
       <c r="K13" t="n">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="L13" t="n">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5827</v>
+        <v>4.2269</v>
       </c>
       <c r="N13" t="n">
-        <v>269</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.5245</v>
+        <v>4.2096</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7998</v>
+        <v>2.1496</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0025</v>
+        <v>1.2332</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5245</v>
+        <v>4.2096</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1013</v>
+        <v>3.0043</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4232</v>
+        <v>1.2053</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1013</v>
+        <v>3.0043</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1157</v>
+        <v>3.0296</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4232</v>
+        <v>1.2053</v>
       </c>
       <c r="K14" t="n">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="L14" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5389</v>
+        <v>4.2349</v>
       </c>
       <c r="N14" t="n">
-        <v>216</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.1028</v>
+        <v>4.209</v>
       </c>
       <c r="C15" t="n">
-        <v>1.5844</v>
+        <v>2.1493</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8321</v>
+        <v>1.233</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1028</v>
+        <v>4.209</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7983</v>
+        <v>2.9045</v>
       </c>
       <c r="G15" t="n">
         <v>1.3045</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7983</v>
+        <v>2.9045</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7983</v>
+        <v>2.9045</v>
       </c>
       <c r="J15" t="n">
         <v>1.3045</v>
@@ -1127,7 +1127,7 @@
         <v>123</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1028</v>
+        <v>4.209</v>
       </c>
       <c r="N15" t="n">
         <v>206</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0471</v>
+        <v>4.1162</v>
       </c>
       <c r="C16" t="n">
-        <v>1.556</v>
+        <v>2.1019</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8096</v>
+        <v>1.196</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0471</v>
+        <v>4.1162</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0856</v>
+        <v>2.1547</v>
       </c>
       <c r="G16" t="n">
         <v>1.9615</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0856</v>
+        <v>2.1547</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0856</v>
+        <v>2.1547</v>
       </c>
       <c r="J16" t="n">
         <v>1.9615</v>
@@ -1173,7 +1173,7 @@
         <v>152</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0471</v>
+        <v>4.1162</v>
       </c>
       <c r="N16" t="n">
         <v>252</v>
@@ -1182,127 +1182,127 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8115</v>
+        <v>3.4918</v>
       </c>
       <c r="C17" t="n">
-        <v>1.4357</v>
+        <v>1.7831</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7144</v>
+        <v>0.9472</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8115</v>
+        <v>3.4918</v>
       </c>
       <c r="F17" t="n">
-        <v>3.8115</v>
+        <v>3.9436</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>-0.4518</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8115</v>
+        <v>3.9436</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8293</v>
+        <v>3.9768</v>
       </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>-0.4518</v>
       </c>
       <c r="K17" t="n">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="L17" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8293</v>
+        <v>3.525</v>
       </c>
       <c r="N17" t="n">
-        <v>283</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6399</v>
+        <v>3.4863</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3481</v>
+        <v>1.7803</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6451</v>
+        <v>0.945</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6399</v>
+        <v>3.4863</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0917</v>
+        <v>4.4863</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4518</v>
+        <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0917</v>
+        <v>4.7315</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1061</v>
+        <v>4.7315</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4518</v>
+        <v>-1</v>
       </c>
       <c r="K18" t="n">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="L18" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6543</v>
+        <v>3.7315</v>
       </c>
       <c r="N18" t="n">
-        <v>216</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.3912</v>
+        <v>2.8668</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2211</v>
+        <v>1.4639</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5446</v>
+        <v>0.6982</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3912</v>
+        <v>2.8668</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8439</v>
+        <v>3.8668</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5473</v>
+        <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8439</v>
+        <v>3.8668</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8525</v>
+        <v>3.8994</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5473</v>
+        <v>-1</v>
       </c>
       <c r="K19" t="n">
         <v>207</v>
@@ -1311,7 +1311,7 @@
         <v>76</v>
       </c>
       <c r="M19" t="n">
-        <v>2.3998</v>
+        <v>2.8994</v>
       </c>
       <c r="N19" t="n">
         <v>283</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0765</v>
+        <v>2.8623</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0604</v>
+        <v>1.4616</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4175</v>
+        <v>0.6964</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0765</v>
+        <v>2.8623</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0765</v>
+        <v>2.8623</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0765</v>
+        <v>2.8623</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0765</v>
+        <v>2.8623</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0765</v>
+        <v>2.8623</v>
       </c>
       <c r="N20" t="n">
         <v>177</v>
@@ -1366,967 +1366,967 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0617</v>
+        <v>2.699</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0528</v>
+        <v>1.3782</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4115</v>
+        <v>0.6314</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0617</v>
+        <v>2.699</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5179</v>
+        <v>1.9483</v>
       </c>
       <c r="G21" t="n">
-        <v>3.5796</v>
+        <v>0.7507</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5179</v>
+        <v>1.9483</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5179</v>
+        <v>1.9647</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5796</v>
+        <v>0.7507</v>
       </c>
       <c r="K21" t="n">
-        <v>105</v>
+        <v>174</v>
       </c>
       <c r="L21" t="n">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0617</v>
+        <v>2.7154</v>
       </c>
       <c r="N21" t="n">
-        <v>239</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8395</v>
+        <v>2.611</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9393</v>
+        <v>1.3333</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3218</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8395</v>
+        <v>2.611</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0888</v>
+        <v>2.0637</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7507</v>
+        <v>0.5473</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0888</v>
+        <v>2.0637</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0939</v>
+        <v>2.0811</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7507</v>
+        <v>0.5473</v>
       </c>
       <c r="K22" t="n">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="L22" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8446</v>
+        <v>2.6284</v>
       </c>
       <c r="N22" t="n">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7086</v>
+        <v>2.4572</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8725000000000001</v>
+        <v>1.2548</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2689</v>
+        <v>0.535</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7086</v>
+        <v>2.4572</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7086</v>
+        <v>2.9116</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.4544</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7086</v>
+        <v>2.9116</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7086</v>
+        <v>2.9116</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.4544</v>
       </c>
       <c r="K23" t="n">
-        <v>190</v>
+        <v>71</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7086</v>
+        <v>2.4572</v>
       </c>
       <c r="N23" t="n">
-        <v>190</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6916</v>
+        <v>2.1295</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8638</v>
+        <v>1.0874</v>
       </c>
       <c r="D24" t="n">
-        <v>0.262</v>
+        <v>0.4045</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6916</v>
+        <v>2.1295</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6916</v>
+        <v>2.1295</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6916</v>
+        <v>2.1295</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6916</v>
+        <v>2.1295</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6916</v>
+        <v>2.1295</v>
       </c>
       <c r="N24" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6457</v>
+        <v>2.0617</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8404</v>
+        <v>1.0528</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2435</v>
+        <v>0.3775</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6457</v>
+        <v>2.0617</v>
       </c>
       <c r="F25" t="n">
-        <v>2.6457</v>
+        <v>-1.5179</v>
       </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>3.5796</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6457</v>
+        <v>-1.5179</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6457</v>
+        <v>-1.5179</v>
       </c>
       <c r="J25" t="n">
-        <v>-1</v>
+        <v>3.5796</v>
       </c>
       <c r="K25" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="L25" t="n">
-        <v>40</v>
+        <v>134</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6457</v>
+        <v>2.0617</v>
       </c>
       <c r="N25" t="n">
-        <v>133</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.5134</v>
+        <v>1.9204</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7728</v>
+        <v>0.9807</v>
       </c>
       <c r="D26" t="n">
-        <v>0.19</v>
+        <v>0.3212</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5134</v>
+        <v>1.9204</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5134</v>
+        <v>2.6752</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.7548</v>
       </c>
       <c r="H26" t="n">
-        <v>1.5134</v>
+        <v>2.6752</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5134</v>
+        <v>2.6752</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.7548</v>
       </c>
       <c r="K26" t="n">
-        <v>195</v>
+        <v>93</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M26" t="n">
-        <v>1.5134</v>
+        <v>1.9204</v>
       </c>
       <c r="N26" t="n">
-        <v>195</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.4115</v>
+        <v>1.8657</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7208</v>
+        <v>0.9527</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1489</v>
+        <v>0.2994</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4115</v>
+        <v>1.8657</v>
       </c>
       <c r="F27" t="n">
-        <v>2.1663</v>
+        <v>2.8657</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.7548</v>
+        <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>2.1663</v>
+        <v>2.8657</v>
       </c>
       <c r="I27" t="n">
-        <v>2.1663</v>
+        <v>2.8657</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.7548</v>
+        <v>-1</v>
       </c>
       <c r="K27" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="L27" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M27" t="n">
-        <v>1.4115</v>
+        <v>1.8657</v>
       </c>
       <c r="N27" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.4014</v>
+        <v>1.7102</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7156</v>
+        <v>0.8733</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1448</v>
+        <v>0.2374</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4014</v>
+        <v>1.7102</v>
       </c>
       <c r="F28" t="n">
-        <v>1.8558</v>
+        <v>1.7102</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4544</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.8558</v>
+        <v>1.7102</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8558</v>
+        <v>1.7102</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4544</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>71</v>
+        <v>190</v>
       </c>
       <c r="L28" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4014</v>
+        <v>1.7102</v>
       </c>
       <c r="N28" t="n">
-        <v>119</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2464</v>
+        <v>1.6916</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6365</v>
+        <v>0.8638</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0822</v>
+        <v>0.23</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2464</v>
+        <v>1.6916</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7848000000000001</v>
+        <v>1.6916</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4616</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7848000000000001</v>
+        <v>1.6916</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7848000000000001</v>
+        <v>1.6916</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4616</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="L29" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2464</v>
+        <v>1.6916</v>
       </c>
       <c r="N29" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.2315</v>
+        <v>1.6387</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6289</v>
+        <v>0.8368</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0761</v>
+        <v>0.2089</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2315</v>
+        <v>1.6387</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2315</v>
+        <v>1.8512</v>
       </c>
       <c r="G30" t="n">
-        <v>-1</v>
+        <v>-0.2125</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2315</v>
+        <v>1.8512</v>
       </c>
       <c r="I30" t="n">
-        <v>2.2315</v>
+        <v>1.8667</v>
       </c>
       <c r="J30" t="n">
-        <v>-1</v>
+        <v>-0.2125</v>
       </c>
       <c r="K30" t="n">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c r="L30" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2315</v>
+        <v>1.6542</v>
       </c>
       <c r="N30" t="n">
-        <v>119</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1667</v>
+        <v>1.5503</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5958</v>
+        <v>0.7917</v>
       </c>
       <c r="D31" t="n">
-        <v>0.05</v>
+        <v>0.1737</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1667</v>
+        <v>1.5503</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1667</v>
+        <v>-0.3002</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.8505</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1667</v>
+        <v>-0.3002</v>
       </c>
       <c r="I31" t="n">
-        <v>1.1667</v>
+        <v>-0.3027</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.8505</v>
       </c>
       <c r="K31" t="n">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1667</v>
+        <v>1.5478</v>
       </c>
       <c r="N31" t="n">
-        <v>131</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1044</v>
+        <v>1.4929</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.7624</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0248</v>
+        <v>0.1509</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1044</v>
+        <v>1.4929</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1044</v>
+        <v>2.4929</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1044</v>
+        <v>2.4929</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1044</v>
+        <v>2.4929</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K32" t="n">
-        <v>195</v>
+        <v>71</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1044</v>
+        <v>1.4929</v>
       </c>
       <c r="N32" t="n">
-        <v>195</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.0015</v>
+        <v>1.4548</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5114</v>
+        <v>0.7429</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0168</v>
+        <v>0.1357</v>
       </c>
       <c r="E33" t="n">
-        <v>1.0015</v>
+        <v>1.4548</v>
       </c>
       <c r="F33" t="n">
-        <v>1.0015</v>
+        <v>2.3185</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.8637</v>
       </c>
       <c r="H33" t="n">
-        <v>1.0015</v>
+        <v>2.3185</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0015</v>
+        <v>2.3185</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.8637</v>
       </c>
       <c r="K33" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M33" t="n">
-        <v>1.0015</v>
+        <v>1.4548</v>
       </c>
       <c r="N33" t="n">
-        <v>74</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9986</v>
+        <v>1.297</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5099</v>
+        <v>0.6623</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.018</v>
+        <v>0.0728</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9986</v>
+        <v>1.297</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8519</v>
+        <v>0.8354</v>
       </c>
       <c r="G34" t="n">
-        <v>1.8505</v>
+        <v>0.4616</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8519</v>
+        <v>0.8354</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8559</v>
+        <v>0.8354</v>
       </c>
       <c r="J34" t="n">
-        <v>1.8505</v>
+        <v>0.4616</v>
       </c>
       <c r="K34" t="n">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="L34" t="n">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9946</v>
+        <v>1.297</v>
       </c>
       <c r="N34" t="n">
-        <v>269</v>
+        <v>206</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9862</v>
+        <v>1.2961</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5036</v>
+        <v>0.6619</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.023</v>
+        <v>0.0725</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9862</v>
+        <v>1.2961</v>
       </c>
       <c r="F35" t="n">
-        <v>1.9862</v>
+        <v>1.2961</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.9862</v>
+        <v>1.2961</v>
       </c>
       <c r="I35" t="n">
-        <v>1.9862</v>
+        <v>1.2961</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>71</v>
+        <v>195</v>
       </c>
       <c r="L35" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9862</v>
+        <v>1.2961</v>
       </c>
       <c r="N35" t="n">
-        <v>119</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>yay</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8891</v>
+        <v>1.1839</v>
       </c>
       <c r="C36" t="n">
-        <v>0.454</v>
+        <v>0.6046</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0622</v>
+        <v>0.0278</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8891</v>
+        <v>1.1839</v>
       </c>
       <c r="F36" t="n">
-        <v>1.1016</v>
+        <v>2.1455</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.2125</v>
+        <v>-0.9616</v>
       </c>
       <c r="H36" t="n">
-        <v>1.1016</v>
+        <v>2.1455</v>
       </c>
       <c r="I36" t="n">
-        <v>1.1067</v>
+        <v>2.1455</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.2125</v>
+        <v>-0.9616</v>
       </c>
       <c r="K36" t="n">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="L36" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8942</v>
+        <v>1.1839</v>
       </c>
       <c r="N36" t="n">
-        <v>216</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>tonyblack</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7954</v>
+        <v>1.1791</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4062</v>
+        <v>0.6021</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1</v>
+        <v>0.0258</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7954</v>
+        <v>1.1791</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7954</v>
+        <v>1.1791</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7954</v>
+        <v>1.1791</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7954</v>
+        <v>1.1791</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7954</v>
+        <v>1.1791</v>
       </c>
       <c r="N37" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7435</v>
+        <v>1.1667</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3797</v>
+        <v>0.5958</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.121</v>
+        <v>0.0209</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7435</v>
+        <v>1.1667</v>
       </c>
       <c r="F38" t="n">
-        <v>1.6072</v>
+        <v>1.1667</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8637</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.6072</v>
+        <v>1.1667</v>
       </c>
       <c r="I38" t="n">
-        <v>1.6072</v>
+        <v>1.1667</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8637</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7434999999999999</v>
+        <v>1.1667</v>
       </c>
       <c r="N38" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yay</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4934</v>
+        <v>1.0015</v>
       </c>
       <c r="C39" t="n">
-        <v>0.252</v>
+        <v>0.5114</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.222</v>
+        <v>-0.0449</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4934</v>
+        <v>1.0015</v>
       </c>
       <c r="F39" t="n">
-        <v>1.455</v>
+        <v>1.0015</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.9616</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.455</v>
+        <v>1.0015</v>
       </c>
       <c r="I39" t="n">
-        <v>1.455</v>
+        <v>1.0015</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9616</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L39" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4934000000000001</v>
+        <v>1.0015</v>
       </c>
       <c r="N39" t="n">
-        <v>119</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tonyblack</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4794</v>
+        <v>0.8351</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2448</v>
+        <v>0.4264</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2277</v>
+        <v>-0.1112</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4794</v>
+        <v>0.8351</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4794</v>
+        <v>0.8351</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4794</v>
+        <v>0.8351</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4794</v>
+        <v>0.8351</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4794</v>
+        <v>0.8351</v>
       </c>
       <c r="N40" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>jR</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3596</v>
+        <v>0.7054</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1836</v>
+        <v>0.3602</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2761</v>
+        <v>-0.1629</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3596</v>
+        <v>0.7054</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9818</v>
+        <v>0.7054</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6222</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9818</v>
+        <v>0.7054</v>
       </c>
       <c r="I41" t="n">
-        <v>0.9818</v>
+        <v>0.7054</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6222</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="L41" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3596</v>
+        <v>0.7054</v>
       </c>
       <c r="N41" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42">
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2779</v>
+        <v>0.7034</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1419</v>
+        <v>0.3592</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3091</v>
+        <v>-0.1637</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2779</v>
+        <v>0.7034</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.12</v>
+        <v>0.3055</v>
       </c>
       <c r="G42" t="n">
         <v>0.3979</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.12</v>
+        <v>0.3055</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1205</v>
+        <v>0.3081</v>
       </c>
       <c r="J42" t="n">
         <v>0.3979</v>
@@ -2369,7 +2369,7 @@
         <v>58</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2774</v>
+        <v>0.706</v>
       </c>
       <c r="N42" t="n">
         <v>216</v>
@@ -2378,265 +2378,265 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>xccurate</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2284</v>
+        <v>0.4166</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1166</v>
+        <v>0.2127</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3291</v>
+        <v>-0.2779</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2284</v>
+        <v>0.4166</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2284</v>
+        <v>1.0388</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.6222</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2284</v>
+        <v>1.0388</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2284</v>
+        <v>1.0388</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.6222</v>
       </c>
       <c r="K43" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2284</v>
+        <v>0.4166</v>
       </c>
       <c r="N43" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kvik</t>
+          <t>xccurate</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1075</v>
+        <v>0.2284</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0549</v>
+        <v>0.1166</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3779</v>
+        <v>-0.3529</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1075</v>
+        <v>0.2284</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1075</v>
+        <v>0.2284</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1075</v>
+        <v>0.2284</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1075</v>
+        <v>0.2284</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1075</v>
+        <v>0.2284</v>
       </c>
       <c r="N44" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1824</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0447</v>
+        <v>0.0931</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.386</v>
+        <v>-0.3712</v>
       </c>
       <c r="E45" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1824</v>
       </c>
       <c r="F45" t="n">
-        <v>0.08749999999999999</v>
+        <v>1.1824</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.08749999999999999</v>
+        <v>1.1824</v>
       </c>
       <c r="I45" t="n">
-        <v>0.08749999999999999</v>
+        <v>1.1824</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K45" t="n">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M45" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1823999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Kvik</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.1095</v>
+        <v>0.1075</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0559</v>
+        <v>0.0549</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4656</v>
+        <v>-0.4011</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.1095</v>
+        <v>0.1075</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.4317</v>
+        <v>0.1075</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3222</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.4317</v>
+        <v>0.1075</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4337</v>
+        <v>0.1075</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3222</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="L46" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.1115</v>
+        <v>0.1075</v>
       </c>
       <c r="N46" t="n">
-        <v>269</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.121</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0618</v>
+        <v>0.0447</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4702</v>
+        <v>-0.4091</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.121</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.121</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.121</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.121</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.121</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>98</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1733</v>
+        <v>0.0023</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0885</v>
+        <v>0.0012</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4914</v>
+        <v>-0.443</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.1733</v>
+        <v>0.0023</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8267</v>
+        <v>0.0092</v>
       </c>
       <c r="G48" t="n">
-        <v>-1</v>
+        <v>-0.0069</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8267</v>
+        <v>0.0092</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8267</v>
+        <v>0.0092</v>
       </c>
       <c r="J48" t="n">
-        <v>-1</v>
+        <v>-0.0069</v>
       </c>
       <c r="K48" t="n">
         <v>93</v>
@@ -2645,7 +2645,7 @@
         <v>40</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1733</v>
+        <v>0.0023</v>
       </c>
       <c r="N48" t="n">
         <v>133</v>
@@ -2654,32 +2654,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1787</v>
+        <v>-0.0391</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4936</v>
+        <v>-0.4595</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1787</v>
+        <v>-0.0391</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1787</v>
+        <v>-0.0391</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1787</v>
+        <v>-0.0391</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1787</v>
+        <v>-0.0391</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1787</v>
+        <v>-0.0391</v>
       </c>
       <c r="N49" t="n">
         <v>177</v>
@@ -2700,277 +2700,277 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>jR</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1996</v>
+        <v>-0.1079</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1019</v>
+        <v>-0.0551</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.502</v>
+        <v>-0.4869</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1996</v>
+        <v>-0.1079</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1996</v>
+        <v>-0.4301</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.3222</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1996</v>
+        <v>-0.4301</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1996</v>
+        <v>-0.4337</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>0.3222</v>
       </c>
       <c r="K50" t="n">
-        <v>97</v>
+        <v>174</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1996</v>
+        <v>-0.1115</v>
       </c>
       <c r="N50" t="n">
-        <v>97</v>
+        <v>269</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2224</v>
+        <v>-0.121</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1136</v>
+        <v>-0.0618</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5112</v>
+        <v>-0.4921</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.2224</v>
+        <v>-0.121</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2155</v>
+        <v>-0.121</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.0069</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2155</v>
+        <v>-0.121</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2155</v>
+        <v>-0.121</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.0069</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="L51" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.2224</v>
+        <v>-0.121</v>
       </c>
       <c r="N51" t="n">
-        <v>133</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2348</v>
+        <v>-0.1787</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1199</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5162</v>
+        <v>-0.5151</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2348</v>
+        <v>-0.1787</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2348</v>
+        <v>-0.1787</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2348</v>
+        <v>-0.1787</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2348</v>
+        <v>-0.1787</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2348</v>
+        <v>-0.1787</v>
       </c>
       <c r="N52" t="n">
-        <v>131</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2456</v>
+        <v>-0.2348</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1254</v>
+        <v>-0.1199</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5206</v>
+        <v>-0.5375</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2456</v>
+        <v>-0.2348</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2456</v>
+        <v>-0.2348</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.2456</v>
+        <v>-0.2348</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2456</v>
+        <v>-0.2348</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.2456</v>
+        <v>-0.2348</v>
       </c>
       <c r="N53" t="n">
-        <v>74</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>jmqa</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2671</v>
+        <v>-0.2456</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1364</v>
+        <v>-0.1254</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5293</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2671</v>
+        <v>-0.2456</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2671</v>
+        <v>-0.2456</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2671</v>
+        <v>-0.2456</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2671</v>
+        <v>-0.2456</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2671</v>
+        <v>-0.2456</v>
       </c>
       <c r="N54" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>jmqa</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2909</v>
+        <v>-0.2671</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1485</v>
+        <v>-0.1364</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5389</v>
+        <v>-0.5503</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2909</v>
+        <v>-0.2671</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2909</v>
+        <v>-0.2671</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2909</v>
+        <v>-0.2671</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2909</v>
+        <v>-0.2671</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2909</v>
+        <v>-0.2671</v>
       </c>
       <c r="N55" t="n">
-        <v>177</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56">
@@ -2986,7 +2986,7 @@
         <v>-0.1548</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5438</v>
+        <v>-0.5647</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3032</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2102</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5877</v>
+        <v>-0.6079</v>
       </c>
       <c r="E57" t="n">
         <v>-0.4117</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2483</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6178</v>
+        <v>-0.6377</v>
       </c>
       <c r="E58" t="n">
         <v>-0.4863</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2954</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6551</v>
+        <v>-0.6744</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5785</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3382</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6889</v>
+        <v>-0.7078</v>
       </c>
       <c r="E60" t="n">
         <v>-0.6623</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3522</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7</v>
+        <v>-0.7187</v>
       </c>
       <c r="E61" t="n">
         <v>-0.6898</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3809</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7227</v>
+        <v>-0.7411</v>
       </c>
       <c r="E62" t="n">
         <v>-0.746</v>
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.8125</v>
+        <v>-0.7729</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4149</v>
+        <v>-0.3947</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7496</v>
+        <v>-0.7518</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.8125</v>
+        <v>-0.7729</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.8125</v>
+        <v>-0.7729</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.8125</v>
+        <v>-0.7729</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.8125</v>
+        <v>-0.7729</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.8125</v>
+        <v>-0.7729</v>
       </c>
       <c r="N63" t="n">
         <v>195</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4331</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.764</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="E64" t="n">
         <v>-0.8481</v>
@@ -3400,7 +3400,7 @@
         <v>-0.477</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7987</v>
+        <v>-0.8161</v>
       </c>
       <c r="E65" t="n">
         <v>-0.9341</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4979</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8153</v>
+        <v>-0.8324</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9751</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.9878</v>
+        <v>-0.9855</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5044</v>
+        <v>-0.5032</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8204</v>
+        <v>-0.8365</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.9878</v>
+        <v>-0.9855</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.6223</v>
+        <v>-0.62</v>
       </c>
       <c r="G67" t="n">
         <v>-0.3655</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.6223</v>
+        <v>-0.62</v>
       </c>
       <c r="I67" t="n">
         <v>-0.6252</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5338000000000001</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8437</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="E68" t="n">
         <v>-1.0454</v>
@@ -3584,7 +3584,7 @@
         <v>-0.6765</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9565</v>
+        <v>-0.9717</v>
       </c>
       <c r="E69" t="n">
         <v>-1.3247</v>
@@ -3630,7 +3630,7 @@
         <v>-0.7258</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-1.0102</v>
       </c>
       <c r="E70" t="n">
         <v>-1.4213</v>
@@ -3676,7 +3676,7 @@
         <v>-0.788</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0447</v>
+        <v>-1.0587</v>
       </c>
       <c r="E71" t="n">
         <v>-1.5431</v>
@@ -3722,7 +3722,7 @@
         <v>-0.8401</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0859</v>
+        <v>-1.0993</v>
       </c>
       <c r="E72" t="n">
         <v>-1.6451</v>
@@ -3768,7 +3768,7 @@
         <v>-0.9226</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1513</v>
+        <v>-1.1637</v>
       </c>
       <c r="E73" t="n">
         <v>-1.8068</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.834</v>
+        <v>-1.8309</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.9365</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1623</v>
+        <v>-1.1733</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.834</v>
+        <v>-1.8309</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.834</v>
+        <v>-0.8309</v>
       </c>
       <c r="G74" t="n">
         <v>-1</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.834</v>
+        <v>-0.8309</v>
       </c>
       <c r="I74" t="n">
         <v>-0.8379</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-2.1383</v>
+        <v>-1.9869</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.0919</v>
+        <v>-1.0146</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2852</v>
+        <v>-1.2355</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.1383</v>
+        <v>-1.9869</v>
       </c>
       <c r="F75" t="n">
-        <v>-2.1383</v>
+        <v>-1.9869</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-2.1383</v>
+        <v>-1.9869</v>
       </c>
       <c r="I75" t="n">
-        <v>-2.1383</v>
+        <v>-1.9869</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-2.1383</v>
+        <v>-1.9869</v>
       </c>
       <c r="N75" t="n">
         <v>177</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-2.1531</v>
+        <v>-2.102</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.0995</v>
+        <v>-1.0734</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2912</v>
+        <v>-1.2813</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.1531</v>
+        <v>-2.102</v>
       </c>
       <c r="F76" t="n">
-        <v>-2.1257</v>
+        <v>-2.0746</v>
       </c>
       <c r="G76" t="n">
         <v>-0.0274</v>
       </c>
       <c r="H76" t="n">
-        <v>-2.1257</v>
+        <v>-2.0746</v>
       </c>
       <c r="I76" t="n">
-        <v>-2.1356</v>
+        <v>-2.0921</v>
       </c>
       <c r="J76" t="n">
         <v>-0.0274</v>
@@ -3933,7 +3933,7 @@
         <v>76</v>
       </c>
       <c r="M76" t="n">
-        <v>-2.163</v>
+        <v>-2.1195</v>
       </c>
       <c r="N76" t="n">
         <v>283</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1357</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3198</v>
+        <v>-1.33</v>
       </c>
       <c r="E77" t="n">
         <v>-2.2241</v>
@@ -3998,7 +3998,7 @@
         <v>-1.1702</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3471</v>
+        <v>-1.3568</v>
       </c>
       <c r="E78" t="n">
         <v>-2.2915</v>
@@ -4044,7 +4044,7 @@
         <v>-1.2051</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3747</v>
+        <v>-1.3841</v>
       </c>
       <c r="E79" t="n">
         <v>-2.36</v>
@@ -4090,7 +4090,7 @@
         <v>-1.219</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3857</v>
+        <v>-1.3949</v>
       </c>
       <c r="E80" t="n">
         <v>-2.3871</v>
@@ -4136,7 +4136,7 @@
         <v>-1.3091</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.457</v>
+        <v>-1.4652</v>
       </c>
       <c r="E81" t="n">
         <v>-2.5636</v>
